--- a/Assets/Scripts/StorySystemPackage/ScriptableObjects/CountAndCook.xlsx
+++ b/Assets/Scripts/StorySystemPackage/ScriptableObjects/CountAndCook.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="168">
   <si>
     <t xml:space="preserve">voiceover_text</t>
   </si>
@@ -284,6 +284,234 @@
   </si>
   <si>
     <t xml:space="preserve">idle_nudge_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s add some cool Ice Cubes!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_IceCube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ice Cubes added! So cool!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_IceCube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now, let’s squeeze in some Lemon Slices!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_LemonSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lemon Slices added! Nice and zesty!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_LemonSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to drop in some juicy Strawberries!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_Strawberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strawberries added! Sweet and juicy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_Strawberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s toss in some crunchy Broccoli!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_BroccoliPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoli added! Nice and crunchy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_BroccoliPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now let’s add some ripe Tomato!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_TomatoPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomato added! Perfectly ripe!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_TomatoPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s sprinkle in some sweet Corn!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_CornPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corn added! So sweet!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_CornPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time for some colorful Bell Pepper!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_BellPepperPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell Pepper added! Such a nice crunch!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_BellPepperPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s start with the Bottom Bread Slice!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_BottomBreadSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottom Bread Slice added! Great start!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_BottomBreadSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now, let’s layer on some Cucumber Slices!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_CucumberSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cucumber Slices added! Nice and fresh!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_CucumberSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s add some juicy Tomato Slices!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_TomatoSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomato Slices added! Yummy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_TomatoSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time for a crisp Lettuce Leaf!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_LettuceLeaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lettuce Leaf added! So crisp!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_LettuceLeaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s finish with the Top Bread Slice!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_TopBreadSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Bread Slice added! Sandwich complete!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_TopBreadSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s squeeze in some Orange Slices!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_OrangeSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange Slices added! Bursting with flavor!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_OrangeSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now, let’s add some sweet Mango Chunks!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_MangoChunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mango Chunks added! So sweet!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_MangoChunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s toss in some crunchy Apple!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_ApplePiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple added! Nice and crunchy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_ApplePiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time for some sweet Banana Slices!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_BananaSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banana Slices added! Yummy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_BananaSlice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s add a handful of juicy Grapes!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_Grapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grapes added! Sweet and juicy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_Grapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now, let’s add some Strawberry Pieces!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_StrawberryPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strawberry Pieces added! Delicious!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_StrawberryPiece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s finish with a Spoon of Yogurt!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_intro_SpoonYogurt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogurt added! Creamy and delicious!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card_outro_SpoonYogurt</t>
   </si>
 </sst>
 </file>
@@ -341,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
@@ -938,6 +1166,538 @@
         <v>91</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="0" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="0" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="0" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="0" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="0" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="0" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="0" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="0" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
